--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,6 +981,218 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118637299</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136951479</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43342</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dockmyr, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537979</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6981108</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951479</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136951481</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98282</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dockmyr, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537979</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6981100</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951481</t>
         </is>
       </c>
     </row>
@@ -989,6 +1201,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136951479</v>
       </c>
       <c r="B5" t="n">
-        <v>43342</v>
+        <v>43355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136951479</v>
       </c>
       <c r="B5" t="n">
-        <v>43355</v>
+        <v>43357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98320</v>
+        <v>98323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136951479</v>
       </c>
       <c r="B5" t="n">
-        <v>43357</v>
+        <v>43367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98323</v>
+        <v>98333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98333</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136951479</v>
       </c>
       <c r="B5" t="n">
-        <v>43367</v>
+        <v>43368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>98363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98363</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35907-2025 artfynd.xlsx
+++ b/artfynd/A 35907-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>136951481</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>98367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
